--- a/excels/game.xlsx
+++ b/excels/game.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="heros" sheetId="2" r:id="rId1"/>
@@ -659,20 +659,7 @@
     <author>asd14</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>加入时间，
-5,10会在5~10s内加入</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -685,7 +672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -703,7 +690,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="268">
   <si>
     <t>id</t>
   </si>
@@ -729,22 +716,28 @@
     <t>3005</t>
   </si>
   <si>
-    <t>0:3005</t>
-  </si>
-  <si>
-    <t>付费</t>
-  </si>
-  <si>
-    <t>0:4</t>
-  </si>
-  <si>
-    <t>免费</t>
-  </si>
-  <si>
-    <t>0:4;1:4</t>
-  </si>
-  <si>
-    <t>6:500</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1:3005</t>
+  </si>
+  <si>
+    <t>3009</t>
+  </si>
+  <si>
+    <t>1:3009</t>
+  </si>
+  <si>
+    <t>3017</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1:3017</t>
+  </si>
+  <si>
+    <t>6:50000</t>
   </si>
   <si>
     <t>itemType</t>
@@ -768,9 +761,6 @@
     <t>6:1</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>10008</t>
   </si>
   <si>
@@ -786,9 +776,6 @@
     <t>6:25000</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>全库透视</t>
   </si>
   <si>
@@ -819,87 +806,87 @@
     <t>6:1000</t>
   </si>
   <si>
+    <t>四象窥视</t>
+  </si>
+  <si>
+    <t>10067</t>
+  </si>
+  <si>
+    <t>6:750</t>
+  </si>
+  <si>
+    <t>宝光四鉴</t>
+  </si>
+  <si>
+    <t>200398</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>6:1688400</t>
+  </si>
+  <si>
+    <t>私人直升机黑匣子</t>
+  </si>
+  <si>
+    <t>200402</t>
+  </si>
+  <si>
+    <t>6:362400</t>
+  </si>
+  <si>
+    <t>可控核聚变电池包</t>
+  </si>
+  <si>
+    <t>200404</t>
+  </si>
+  <si>
+    <t>6:68800</t>
+  </si>
+  <si>
+    <t>全集成AI自动驾驶系统</t>
+  </si>
+  <si>
+    <t>200407</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>6:101400</t>
+  </si>
+  <si>
+    <t>氢燃料电池堆栈</t>
+  </si>
+  <si>
+    <t>200410</t>
+  </si>
+  <si>
+    <t>6:45231</t>
+  </si>
+  <si>
+    <t>气压盘式制动器</t>
+  </si>
+  <si>
+    <t>200414</t>
+  </si>
+  <si>
+    <t>6:25875</t>
+  </si>
+  <si>
+    <t>赛车方向盘</t>
+  </si>
+  <si>
+    <t>200416</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>四象窥视</t>
-  </si>
-  <si>
-    <t>10067</t>
-  </si>
-  <si>
-    <t>6:750</t>
-  </si>
-  <si>
-    <t>宝光四鉴</t>
-  </si>
-  <si>
-    <t>200398</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>6:1688400</t>
-  </si>
-  <si>
-    <t>私人直升机黑匣子</t>
-  </si>
-  <si>
-    <t>200402</t>
-  </si>
-  <si>
-    <t>6:362400</t>
-  </si>
-  <si>
-    <t>可控核聚变电池包</t>
-  </si>
-  <si>
-    <t>200404</t>
-  </si>
-  <si>
-    <t>6:68800</t>
-  </si>
-  <si>
-    <t>全集成AI自动驾驶系统</t>
-  </si>
-  <si>
-    <t>200407</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>6:101400</t>
-  </si>
-  <si>
-    <t>氢燃料电池堆栈</t>
-  </si>
-  <si>
-    <t>200410</t>
-  </si>
-  <si>
-    <t>6:45231</t>
-  </si>
-  <si>
-    <t>气压盘式制动器</t>
-  </si>
-  <si>
-    <t>200414</t>
-  </si>
-  <si>
-    <t>6:25875</t>
-  </si>
-  <si>
-    <t>赛车方向盘</t>
-  </si>
-  <si>
-    <t>200416</t>
-  </si>
-  <si>
     <t>6:22064</t>
   </si>
   <si>
@@ -1407,24 +1394,6 @@
     <t>cPrePQ</t>
   </si>
   <si>
-    <t>显示所有藏品的轮廓</t>
-  </si>
-  <si>
-    <t>显示所有藏品的品质</t>
-  </si>
-  <si>
-    <t>随机显示4件藏品</t>
-  </si>
-  <si>
-    <t>随机显示4件藏品轮廓</t>
-  </si>
-  <si>
-    <t>随机显示4件藏品的品质</t>
-  </si>
-  <si>
-    <t>显示一个最大面积的品质</t>
-  </si>
-  <si>
     <t>roomType</t>
   </si>
   <si>
@@ -1458,57 +1427,75 @@
     <t>earlyTermination</t>
   </si>
   <si>
-    <t>6:10</t>
-  </si>
-  <si>
-    <t>0,1,2,3,4</t>
-  </si>
-  <si>
-    <t>6000</t>
-  </si>
-  <si>
-    <t>200398,200402,200404,200407,200410,200414,200416,200420</t>
+    <t>robotList</t>
+  </si>
+  <si>
+    <t>6:0</t>
+  </si>
+  <si>
+    <t>6:10000</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>200398,200402,200404,200407,200410,200414,200416,200420,200424,200427,200432,200437,200438,200444,200448,200449,200455,200458,200277,200280,200286,200289,200293,200299,200301,200307,200308,200310,200316,200317,200322,200327,200330,200333,200336,200340,200164,200167,200169,200171,200175,200179,200180,200183,200189,200191,200196,200199,200202,200206,200210,200214,200217,200221</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>100,75,50,25,1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>6:2000</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>100,75,50,25,1</t>
   </si>
   <si>
+    <t>6:5000</t>
+  </si>
+  <si>
+    <t>6:200000</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>rewardMap</t>
   </si>
   <si>
     <t>rewardType</t>
   </si>
   <si>
-    <t>6:100000;10008:100</t>
-  </si>
-  <si>
-    <t>6:100001</t>
-  </si>
-  <si>
-    <t>6:100002</t>
-  </si>
-  <si>
-    <t>6:100003</t>
-  </si>
-  <si>
-    <t>6:100004</t>
-  </si>
-  <si>
-    <t>6:100005</t>
-  </si>
-  <si>
     <t>robotType</t>
   </si>
   <si>
-    <t>roomTypeList</t>
-  </si>
-  <si>
     <t>characterList</t>
   </si>
   <si>
-    <t>joinTimes</t>
-  </si>
-  <si>
     <t>thinkTimes</t>
   </si>
   <si>
@@ -1518,13 +1505,13 @@
     <t>3005,3009,3017</t>
   </si>
   <si>
-    <t>5,10</t>
-  </si>
-  <si>
     <t>10,15</t>
   </si>
   <si>
     <t>30</t>
+  </si>
+  <si>
+    <t>3005,3009</t>
   </si>
 </sst>
 </file>
@@ -1550,6 +1537,18 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1562,8 +1561,9 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1579,21 +1579,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFDE3C36"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
@@ -2225,53 +2212,53 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2798,14 +2785,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="44.5" customWidth="1"/>
     <col min="4" max="4" width="12.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2829,74 +2816,60 @@
       </c>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:11">
-      <c r="A2" s="14" t="s">
+    <row r="2" ht="15" customHeight="1" spans="1:9">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15">
-        <v>1</v>
-      </c>
-      <c r="K2" s="7" t="s">
+      <c r="C2" s="17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:11">
-      <c r="A3" s="14">
-        <v>3009</v>
-      </c>
-      <c r="B3" s="15">
-        <v>0</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:9">
+      <c r="A3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7" t="s">
+      <c r="B3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:11">
-      <c r="A4" s="17">
-        <v>3017</v>
-      </c>
-      <c r="B4" s="15">
-        <v>1</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" ht="16.5" spans="1:9">
+      <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="7"/>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="B4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -2906,7 +2879,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:9">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -2916,7 +2889,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:9">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -2926,7 +2899,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:9">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -2936,7 +2909,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:9">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2946,7 +2919,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:9">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -2956,7 +2929,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:9">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2966,7 +2939,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:9">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2976,7 +2949,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:9">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -2986,7 +2959,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:9">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2996,7 +2969,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:9">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -3006,7 +2979,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:9">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -3034,1465 +3007,1465 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:8">
-      <c r="A2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="12"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:8">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:8">
+      <c r="A4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:8">
-      <c r="A3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:8">
+      <c r="A5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:8">
+      <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:8">
+      <c r="A7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:8">
+      <c r="A8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" ht="24" spans="1:8">
+      <c r="A9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:8">
+      <c r="A10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:8">
+      <c r="A11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="D11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:8">
+      <c r="A12" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:8">
+      <c r="A13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:8">
+      <c r="A14" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:8">
+      <c r="A15" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:8">
+      <c r="A16" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:8">
-      <c r="A4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="E16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:8">
+      <c r="A17" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:8">
+      <c r="A18" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:8">
+      <c r="A19" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:8">
+      <c r="A20" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:8">
+      <c r="A21" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:8">
+      <c r="A22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:8">
+      <c r="A23" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:8">
+      <c r="A24" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:8">
+      <c r="A25" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:8">
+      <c r="A26" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:8">
+      <c r="A27" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:8">
+      <c r="A28" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:8">
+      <c r="A29" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:8">
-      <c r="A5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D29" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="16" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:8">
+      <c r="A30" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:8">
+      <c r="A31" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:8">
+      <c r="A32" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:8">
+      <c r="A33" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:8">
+      <c r="A34" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:8">
+      <c r="A35" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D35" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:8">
+      <c r="A36" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:8">
+      <c r="A37" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:8">
+      <c r="A38" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:8">
+      <c r="A39" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="4"/>
+      <c r="H39" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:8">
+      <c r="A40" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="4"/>
+      <c r="H40" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:8">
+      <c r="A41" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="H41" s="16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:8">
+      <c r="A42" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="4"/>
+      <c r="H42" s="16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:8">
+      <c r="A43" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="4"/>
+      <c r="H43" s="16" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:8">
+      <c r="A44" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="16" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:8">
+      <c r="A45" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:8">
+      <c r="A46" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:8">
+      <c r="A47" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="D47" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="16" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:8">
+      <c r="A48" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:8">
+      <c r="A49" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="4"/>
+      <c r="H49" s="16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:8">
+      <c r="A50" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="4"/>
+      <c r="H50" s="16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:8">
+      <c r="A51" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="4"/>
+      <c r="H51" s="16" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:8">
+      <c r="A52" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="H52" s="16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:8">
+      <c r="A53" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:8">
-      <c r="A6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:8">
-      <c r="A7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="D53" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:8">
+      <c r="A54" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:8">
+      <c r="A55" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:8">
+      <c r="A56" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:8">
-      <c r="A8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="D56" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:8">
+      <c r="A57" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" ht="24" spans="1:8">
-      <c r="A9" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:8">
-      <c r="A10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:8">
-      <c r="A11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="E57" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="H57" s="16" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:8">
+      <c r="A58" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:8">
-      <c r="A12" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:8">
-      <c r="A13" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:8">
-      <c r="A14" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:8">
-      <c r="A15" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:8">
-      <c r="A16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:8">
-      <c r="A17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:8">
-      <c r="A18" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:8">
-      <c r="A19" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:8">
-      <c r="A20" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:8">
-      <c r="A21" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:8">
-      <c r="A22" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:8">
-      <c r="A23" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:8">
-      <c r="A24" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:8">
-      <c r="A25" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:8">
-      <c r="A26" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:8">
-      <c r="A27" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:8">
-      <c r="A28" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:8">
-      <c r="A29" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="13" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:8">
-      <c r="A30" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:8">
-      <c r="A31" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:8">
-      <c r="A32" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G32" s="7"/>
-      <c r="H32" s="13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:8">
-      <c r="A33" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="13" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:8">
-      <c r="A34" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G34" s="7"/>
-      <c r="H34" s="13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:8">
-      <c r="A35" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="13" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:8">
-      <c r="A36" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G36" s="7"/>
-      <c r="H36" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:8">
-      <c r="A37" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G37" s="7"/>
-      <c r="H37" s="13" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:8">
-      <c r="A38" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G38" s="7"/>
-      <c r="H38" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:8">
-      <c r="A39" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G39" s="7"/>
-      <c r="H39" s="13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:8">
-      <c r="A40" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G40" s="7"/>
-      <c r="H40" s="13" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:8">
-      <c r="A41" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G41" s="7"/>
-      <c r="H41" s="13" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:8">
-      <c r="A42" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="13" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:8">
-      <c r="A43" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G43" s="7"/>
-      <c r="H43" s="13" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:8">
-      <c r="A44" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G44" s="7"/>
-      <c r="H44" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:8">
-      <c r="A45" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G45" s="7"/>
-      <c r="H45" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:8">
-      <c r="A46" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G46" s="7"/>
-      <c r="H46" s="13" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:8">
-      <c r="A47" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G47" s="7"/>
-      <c r="H47" s="13" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:8">
-      <c r="A48" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G48" s="7"/>
-      <c r="H48" s="13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:8">
-      <c r="A49" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G49" s="7"/>
-      <c r="H49" s="13" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:8">
-      <c r="A50" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G50" s="7"/>
-      <c r="H50" s="13" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:8">
-      <c r="A51" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G51" s="7"/>
-      <c r="H51" s="13" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:8">
-      <c r="A52" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G52" s="7"/>
-      <c r="H52" s="13" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:8">
-      <c r="A53" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G53" s="7"/>
-      <c r="H53" s="13" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:8">
-      <c r="A54" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G54" s="7"/>
-      <c r="H54" s="13" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:8">
-      <c r="A55" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G55" s="7"/>
-      <c r="H55" s="13" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:8">
-      <c r="A56" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G56" s="7"/>
-      <c r="H56" s="13" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="57" ht="16.5" spans="1:8">
-      <c r="A57" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G57" s="7"/>
-      <c r="H57" s="13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:8">
-      <c r="A58" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E58" s="7" t="s">
+      <c r="D58" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G58" s="7"/>
-      <c r="H58" s="13" t="s">
+      <c r="F58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="16" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:8">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D59" s="7" t="s">
+      <c r="B59" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G59" s="7"/>
-      <c r="H59" s="13" t="s">
+      <c r="F59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="16" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:8">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B60" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D60" s="7" t="s">
+      <c r="B60" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="F60" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G60" s="7"/>
-      <c r="H60" s="13" t="s">
+      <c r="F60" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="16" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="61" ht="16.5" spans="1:8">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B61" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="7" t="s">
+      <c r="B61" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G61" s="7"/>
-      <c r="H61" s="13" t="s">
+      <c r="F61" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="16" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4506,8 +4479,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="12.775" customWidth="1"/>
     <col min="4" max="4" width="13.5583333333333" customWidth="1"/>
@@ -4517,10 +4490,9 @@
     <col min="9" max="9" width="26.3333333333333" customWidth="1"/>
     <col min="10" max="12" width="25.4416666666667" customWidth="1"/>
     <col min="13" max="13" width="19.1083333333333" customWidth="1"/>
-    <col min="14" max="14" width="29.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4561,338 +4533,332 @@
         <v>233</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:16">
-      <c r="A2" s="2">
+    <row r="2" ht="16.5" spans="1:13">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="7">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7">
+        <v>0</v>
+      </c>
+      <c r="M2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:13">
+      <c r="A3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="7">
+        <v>0</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7">
         <v>1</v>
       </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:16">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="F3" s="7">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7">
+        <v>0</v>
+      </c>
+      <c r="L3" s="7">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:13">
+      <c r="A4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="7">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="F3" s="2">
+      <c r="H4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:13">
+      <c r="A5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="7">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
         <v>1</v>
       </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:16">
-      <c r="A4" s="2">
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:13">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="7">
+        <v>4</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="C7" s="7">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
         <v>1</v>
       </c>
-      <c r="F4" s="2">
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
+        <v>6</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>10</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="7">
         <v>1</v>
       </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:16">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="C9" s="7">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
         <v>1</v>
       </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>0</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:16">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>0</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="7" ht="36" spans="1:16">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="G9" s="7">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <v>8</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7">
         <v>-1</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="P7" s="5"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:16">
-      <c r="A8" s="2">
-        <v>3005</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>234</v>
+      <c r="M9" s="7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4905,125 +4871,173 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
     <col min="3" max="3" width="24.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.3333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="38.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.775" style="1" customWidth="1"/>
     <col min="7" max="7" width="30.25" style="1" customWidth="1"/>
     <col min="8" max="9" width="30.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="27.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="27.125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="12" max="12" width="15" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" ht="175.5" spans="1:12">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="D2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="5" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="J2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="L2" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" ht="175.5" spans="1:12">
+      <c r="A3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="C3" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="K3" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="L3" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" ht="175.5" spans="1:12">
+      <c r="A4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
+      <c r="C4" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="F4" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>255</v>
+      <c r="L4" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5036,8 +5050,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="32.375" customWidth="1"/>
     <col min="3" max="3" width="24.375" customWidth="1"/>
@@ -5048,97 +5062,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="A3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3">
         <v>3</v>
       </c>
     </row>
@@ -5152,56 +5100,56 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="11.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="33.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.25" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="2" max="2" width="33.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.25" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>160</v>
+        <v>264</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>273</v>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
